--- a/data/derived_data/6_NMI_CCA/Dataset_2/CCA_NULL_16S_D2.xlsx
+++ b/data/derived_data/6_NMI_CCA/Dataset_2/CCA_NULL_16S_D2.xlsx
@@ -416,7 +416,7 @@
         <v>1.33158747778634</v>
       </c>
       <c r="E2" t="n">
-        <v>0.274</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +433,7 @@
         <v>5.08030680642235</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="4">

--- a/data/derived_data/6_NMI_CCA/Dataset_2/CCA_NULL_16S_D2.xlsx
+++ b/data/derived_data/6_NMI_CCA/Dataset_2/CCA_NULL_16S_D2.xlsx
@@ -416,7 +416,7 @@
         <v>1.33158747778634</v>
       </c>
       <c r="E2" t="n">
-        <v>0.247</v>
+        <v>0.2616</v>
       </c>
     </row>
     <row r="3">
@@ -427,10 +427,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.971978457272574</v>
+        <v>0.971978457272573</v>
       </c>
       <c r="D3" t="n">
-        <v>5.08030680642235</v>
+        <v>5.08030680642234</v>
       </c>
       <c r="E3" t="n">
         <v>0.001</v>
@@ -447,10 +447,10 @@
         <v>1.32967305026129</v>
       </c>
       <c r="D4" t="n">
-        <v>6.02727778832863</v>
+        <v>6.02727778832864</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +464,7 @@
         <v>0.357694592988712</v>
       </c>
       <c r="D5" t="n">
-        <v>5.13951489142407</v>
+        <v>5.13951489142408</v>
       </c>
       <c r="E5" t="n">
         <v>0.003</v>
@@ -484,7 +484,7 @@
         <v>7.24326720244797</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
     </row>
   </sheetData>

--- a/data/derived_data/6_NMI_CCA/Dataset_2/CCA_NULL_16S_D2.xlsx
+++ b/data/derived_data/6_NMI_CCA/Dataset_2/CCA_NULL_16S_D2.xlsx
@@ -416,7 +416,7 @@
         <v>1.33158747778634</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2616</v>
+        <v>0.2626</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         <v>5.13951489142408</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="6">
